--- a/output/Results - sem1.xlsx
+++ b/output/Results - sem1.xlsx
@@ -385,24 +385,24 @@
     <t>230449</t>
   </si>
   <si>
+    <t>230077</t>
+  </si>
+  <si>
+    <t>230444</t>
+  </si>
+  <si>
+    <t>230727</t>
+  </si>
+  <si>
+    <t>230238</t>
+  </si>
+  <si>
+    <t>230052</t>
+  </si>
+  <si>
     <t>230581</t>
   </si>
   <si>
-    <t>230077</t>
-  </si>
-  <si>
-    <t>230444</t>
-  </si>
-  <si>
-    <t>230727</t>
-  </si>
-  <si>
-    <t>230238</t>
-  </si>
-  <si>
-    <t>230052</t>
-  </si>
-  <si>
     <t>28(24.3%)</t>
   </si>
   <si>
@@ -448,7 +448,7 @@
     <t>11(9.6%)</t>
   </si>
   <si>
-    <t>9(7.8%)</t>
+    <t>8(7.0%)</t>
   </si>
   <si>
     <t>13(11.3%)</t>
@@ -460,10 +460,10 @@
     <t>1(0.9%)</t>
   </si>
   <si>
+    <t>2(1.7%)</t>
+  </si>
+  <si>
     <t>0(0.0%)</t>
-  </si>
-  <si>
-    <t>2(1.7%)</t>
   </si>
   <si>
     <t>B-</t>
@@ -1063,10 +1063,10 @@
         <v>147</v>
       </c>
       <c r="P5" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q5" t="s">
         <v>148</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>149</v>
       </c>
       <c r="R5" t="s">
         <v>147</v>
@@ -1104,22 +1104,22 @@
         <v>106</v>
       </c>
       <c r="M6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O6" t="s">
         <v>147</v>
       </c>
       <c r="P6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q6" t="s">
         <v>147</v>
       </c>
       <c r="R6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1154,22 +1154,22 @@
         <v>150</v>
       </c>
       <c r="M7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1204,22 +1204,22 @@
         <v>151</v>
       </c>
       <c r="M8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1254,22 +1254,22 @@
         <v>152</v>
       </c>
       <c r="M9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1304,22 +1304,22 @@
         <v>153</v>
       </c>
       <c r="M10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1354,22 +1354,22 @@
         <v>154</v>
       </c>
       <c r="M11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1404,22 +1404,22 @@
         <v>155</v>
       </c>
       <c r="M12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1454,22 +1454,22 @@
         <v>156</v>
       </c>
       <c r="M13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1504,22 +1504,22 @@
         <v>157</v>
       </c>
       <c r="M14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1554,22 +1554,22 @@
         <v>158</v>
       </c>
       <c r="M15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -4335,51 +4335,51 @@
         <v>123</v>
       </c>
       <c r="C111" t="s">
-        <v>12</v>
+        <v>106</v>
       </c>
       <c r="D111" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F111" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="G111" t="s">
         <v>12</v>
       </c>
       <c r="H111" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="I111">
-        <v>3.792</v>
+        <v>3.785</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B112" t="s">
         <v>124</v>
       </c>
       <c r="C112" t="s">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="D112" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="E112" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F112" t="s">
         <v>12</v>
       </c>
       <c r="G112" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="H112" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="I112">
         <v>3.785</v>
@@ -4387,16 +4387,16 @@
     </row>
     <row r="113" spans="1:9">
       <c r="A113">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B113" t="s">
         <v>125</v>
       </c>
       <c r="C113" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="D113" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="E113" t="s">
         <v>12</v>
@@ -4405,10 +4405,10 @@
         <v>12</v>
       </c>
       <c r="G113" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="H113" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="I113">
         <v>3.785</v>
@@ -4416,13 +4416,13 @@
     </row>
     <row r="114" spans="1:9">
       <c r="A114">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B114" t="s">
         <v>126</v>
       </c>
       <c r="C114" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D114" t="s">
         <v>12</v>
@@ -4431,16 +4431,16 @@
         <v>12</v>
       </c>
       <c r="F114" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="G114" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="H114" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I114">
-        <v>3.785</v>
+        <v>3.764</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -4451,25 +4451,25 @@
         <v>127</v>
       </c>
       <c r="C115" t="s">
+        <v>12</v>
+      </c>
+      <c r="D115" t="s">
+        <v>64</v>
+      </c>
+      <c r="E115" t="s">
         <v>96</v>
       </c>
-      <c r="D115" t="s">
-        <v>12</v>
-      </c>
-      <c r="E115" t="s">
-        <v>12</v>
-      </c>
       <c r="F115" t="s">
         <v>64</v>
       </c>
       <c r="G115" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="H115" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="I115">
-        <v>3.764</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -4486,19 +4486,19 @@
         <v>64</v>
       </c>
       <c r="E116" t="s">
+        <v>12</v>
+      </c>
+      <c r="F116" t="s">
         <v>96</v>
       </c>
-      <c r="F116" t="s">
-        <v>64</v>
-      </c>
       <c r="G116" t="s">
         <v>12</v>
       </c>
       <c r="H116" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="I116">
-        <v>3.75</v>
+        <v>3.735</v>
       </c>
     </row>
   </sheetData>
